--- a/Dulieutruyxuat/So sánh.xlsx
+++ b/Dulieutruyxuat/So sánh.xlsx
@@ -1,50 +1,20 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>2</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="2" baseType="lpstr">
-      <vt:lpstr>DANH SÁCH 560 NGƯỜI DEV XUẤT VỀ</vt:lpstr>
-      <vt:lpstr>200 người đã chuẩn</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <Company/>
-  <Manager/>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="DANH SÁCH 560 NGƯỜI DEV XUẤT VỀ" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="200 người đã chuẩn" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="KẾT QUẢ 200 vs 560" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Ban đầu" state="visible" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="171027"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>Unknown</dc:creator>
-  <dc:title/>
-  <dc:subject/>
-  <dc:description/>
-  <cp:keywords/>
-  <cp:category/>
-  <cp:lastModifiedBy>Unknown</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-17T10:17:03Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-17T10:17:03Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3200" uniqueCount="2570">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="2741">
   <si>
     <t>stt</t>
   </si>
@@ -7768,12 +7738,534 @@
   <si>
     <t>Ảnh mờ không render được</t>
   </si>
+  <si>
+    <t>KẾT QUẢ ĐỐI CHIẾU NGƯỜI TRONG TAB 200 VỚI DANH SÁCH 560</t>
+  </si>
+  <si>
+    <t>Tổng 24 người | Có trong 560: 17 | Cần kiểm tra: 1 | Không tìm thấy: 6</t>
+  </si>
+  <si>
+    <t>Xanh = có trong 560; vàng = tên gần giống cần xác nhận; đỏ = chưa tìm thấy. Ưu tiên kết quả khớp bằng link GAB.</t>
+  </si>
+  <si>
+    <t>TÊN TRONG TAB 200</t>
+  </si>
+  <si>
+    <t>KẾT QUẢ</t>
+  </si>
+  <si>
+    <t>TÊN TƯƠNG ỨNG TRONG 560</t>
+  </si>
+  <si>
+    <t>LINK GAB TAB 200</t>
+  </si>
+  <si>
+    <t>LINK GAB TRONG 560</t>
+  </si>
+  <si>
+    <t>CĂN CỨ ĐỐI CHIẾU</t>
+  </si>
+  <si>
+    <t>GHI CHÚ</t>
+  </si>
+  <si>
+    <t>CẦN KIỂM TRA</t>
+  </si>
+  <si>
+    <t>Tên gần giống 86%</t>
+  </si>
+  <si>
+    <t>Không tự kết luận là cùng người; cần kiểm tra thủ công.</t>
+  </si>
+  <si>
+    <t>CÓ TRONG DANH SÁCH 560</t>
+  </si>
+  <si>
+    <t>Trùng chính xác link GAB</t>
+  </si>
+  <si>
+    <t>Đúng cùng một hồ sơ GAB.</t>
+  </si>
+  <si>
+    <t>KHÔNG TÌM THẤY TRONG 560</t>
+  </si>
+  <si>
+    <t>Không có link hoặc tên khớp đủ chắc</t>
+  </si>
+  <si>
+    <t>Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
+  </si>
+  <si>
+    <t>link gab</t>
+  </si>
+  <si>
+    <t>KLG</t>
+  </si>
+  <si>
+    <t>RÀ SOÁT THÀNH TỰU</t>
+  </si>
+  <si>
+    <t>VIỆT NAM</t>
+  </si>
+  <si>
+    <t>QUỐC TẾ</t>
+  </si>
+  <si>
+    <t>DUYỆT</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/LmSTvVTC7fZfbzR4SxGrlumgme82</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ - Kỷ lục gia Phan Thanh Tiến</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/L2MgnORN8AQ0p9BScplwe3LV2792</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Bùi Văn Ngợi</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phan Thanh Nhiên</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/1tztfUI2VLMHzqoxAshwoxb84qO2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Mậu Linh</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/gg7H0Gu5BNdJryQHh92JK9vHccV2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Trần Văn Anh (Ngọc Minh)</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/n3RY3PnKwheZf3gP8fhS1OoQ9j03</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Thành Tâm</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/tK4zzIhtRIX9G9oPywFxNY5ciSw2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Quang Vũ</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/vAnSgIWi4LXUvh9E3IxNrzneGdA2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thanh Hằng - Thanh Hà</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/eggcPVybrzYNHwaVyniBSvTSjDr2</t>
+  </si>
+  <si>
+    <t>Anh hùng Lao động, Kỷ lục gia Châu Á – Họa sĩ Đặng Ái Việt</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/fRvf9rbC4fbXlLUxZQ5S51kjvEk2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Võ Văn Hải</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Hoàng Thành Lâm</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/TbcQDsHACpTBJHv6ayyMM65XltH2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Trần Bích</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/qNhQLWUURvYC60ZK77zzSBCz4RW2</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Nhà sưu tập Huỳnh Tấn Thành</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/bank/FPavU8TRffMSh1aDhYJmM9kBwzq1</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Cao Văn Long</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Tuệ Chiếu</t>
+  </si>
+  <si>
+    <t>https://gab.world/vi/search?type=klg&amp;search=tu%E1%BB%87%20chi%E1%BA%BFu</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thái Tuệ (vợ ông Tuệ Chiếu)</t>
+  </si>
+  <si>
+    <t>Họa sĩ Vi Quốc Hiệp</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Nhạc sĩ Nguyễn Văn Chung</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Ánh Viên</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Nhà sưu tập Phùng Đại Hùng</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phạm Hoàng Thắng</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Thành Công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kỷ lục gia Hồ Ngọc Hiếu
+(Bút danh Hồn Lửa Việt)</t>
+  </si>
+  <si>
+    <t>Giáo sư - Võ sư, Kỷ lục gia Ngô Xuân Bính</t>
+  </si>
+  <si>
+    <t>Họa sĩ, Kỷ lục gia Trần Đạt</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thế giới Đinh Công Tường</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Lương Hiệu</t>
+  </si>
+  <si>
+    <t>Giáo sư, Kỷ lục gia Vũ Gia Hiền</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Trương Nhị Hà</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Vũ Mạnh Tư</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ ảo thuật, Kỷ lục gia Hoàng Lộc</t>
+  </si>
+  <si>
+    <t>Nghệ nhân Trần Văn Mạnh</t>
+  </si>
+  <si>
+    <t>GS.TS.Kỷ lục gia Cao Ngọc Lân</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Huy Du</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Sỹ Hồ</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Trần Quốc Ẩn</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Tôn Nữ Minh Nhơn</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Quốc Toàn</t>
+  </si>
+  <si>
+    <t>Nhà văn, Kỷ lục gia Trúc Phương</t>
+  </si>
+  <si>
+    <t>Nghệ nhân, Kỷ lục gia PHÙNG HỮU THÁI</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phan Huỳnh Anh</t>
+  </si>
+  <si>
+    <t>Nhà điêu khắc, Kỷ lục gia Đoàn Xuân Hùng</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thế giới Đặng Ngọc Phương Trinh</t>
+  </si>
+  <si>
+    <t>Nghệ nhân, Kỷ lục gia LÊ XUÂN TUNG</t>
+  </si>
+  <si>
+    <t>Nghệ nhân, Kỷ lục gia LÊ XUÂN TÙNG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Châu Thành Toàn</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia - Nhà sưu tập HUỲNH MINH HIỆP</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phạm Trọng Nghĩa</t>
+  </si>
+  <si>
+    <t>Nghệ nhân - Kỷ lục gia Trần Cường Thịnh</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Ngô Vương Việt</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Thạnh</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia La Như Long</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Duy Khang</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Phúc Đức</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Văn Nghỉ</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Văn Mai</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phan Thành Trung</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thế giới, Nhà sưu tập Nguyễn Văn Phúng</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Văn Thiện</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Trọng Huy</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Nguyễn Ái Quỳnh</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Thị Lệ Hạnh</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Lê Duy Thiện</t>
+  </si>
+  <si>
+    <t>Nghệ nhân TRẦN THỊ THU</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Phạm Lê Quốc Cường</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN PHƯỚC LỘC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kỷ lục gia NGUYỄN ĐỨC TÀI
+(TÀI ALEX)</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia TRẦN ANH ĐIỀN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Hùng Cường</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN XUÂN QUANG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia châu Á Nguyễn Thanh Sử</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Trần Quang Huy</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Thế giới, Nhà thư pháp VŨ ĐĂNG HỌC</t>
+  </si>
+  <si>
+    <t>Nhà văn, Kỷ lục gia Lại Văn Long</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Trường Tiến</t>
+  </si>
+  <si>
+    <t>Thạc sỹ, Kỷ lục gia NGUYỄN VĂN VŨ AN</t>
+  </si>
+  <si>
+    <t>Nghệ nhân LÊ ĐẮC NGUYÊN XUÂN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Thanh Thảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Họa sĩ, Nghệ sĩ NGUYỄN VĂN NHÂN
+(Nghệ danh NGUYỄN THẾ NHÂN)</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Đoàn Văn Đức</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN VĂN BUÔI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kỷ lục gia PHẠM THỊ TRÚC THI
+(Bút danh: TRÚC THY)</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Bác sĩ ĐỖ XUÂN TRƯỜNG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN QUỐC HỌC</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia TRẦN PHƯƠNG THẮNG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia VÕ VĂN TÂM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kỷ lục gia HỒ TẤT VÀ
+&amp; Phu nhân</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia TRẦN THANH PHONG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia LÊ ĐÌNH PHÚ</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ - Kỷ lục gia NGUYỄN TIẾN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Nhà thơ PHẠM BÁ NHƠN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN ĐĂNG TÂM</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia NGUYỄN HỮU ĐỈNH</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia SƠN KIỀU PHONG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia HUỲNH MINH VƯƠNG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia ĐINH VĂN TRỌNG</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia -  Kiến trúc sư Nguyễn Thanh Hải</t>
+  </si>
+  <si>
+    <t>Nhạc sĩ, ca sĩ, Kỷ lục gia LÊ ANH TUẤN</t>
+  </si>
+  <si>
+    <t>Nhà sưu tập, Kỷ lục gia LA HƯNG</t>
+  </si>
+  <si>
+    <t>Nhạc sĩ, Kỷ lục gia PHẠM HỮU TÂM</t>
+  </si>
+  <si>
+    <t>Đại tá, Nhà báo, Kỷ lục gia TRẦN THẾ TUYỂN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia, Lương y NGUYỄN BÁ NHO</t>
+  </si>
+  <si>
+    <t>Họa sĩ, Kỷ lục gia BÙI VĂN TOẢN</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia LÊ MINH PHÚ (LÊ PHÚ)</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia Nguyễn Văn Hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thầy Nguyễn Minh Hoàng
+Quản lý Đội Nhạc kèn Võ Thành Trang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Họa sĩ, Kỷ lục gia HOÀNG NGỌC TRÚC
+(Nghệ danh HOÀNG TRÚC)</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ Nhân dân NGUYỄN THỊ THU HUYỀN</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ nhiếp ảnh, Kỷ lục gia NGUYỄN TRƯỜNG SINH</t>
+  </si>
+  <si>
+    <t>Đạo diễn, Kỷ lục gia ĐẶNG MINH HÙNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiến sĩ, Bác sĩ, Kỷ lục gia NGUYỄN HOÀNG ĐỨC
+Trưởng khoa Tiết niệu, Trung tâm Tiết niệu - Thận học - Nam khoa, Bệnh viện Đa khoa Tâm Anh TP.HCM</t>
+  </si>
+  <si>
+    <t>Kỷ lục gia THÁI HỮU NGHĨA</t>
+  </si>
+  <si>
+    <t>Ông NGUYỄN NHỰT VINH</t>
+  </si>
+  <si>
+    <t>Nghệ sĩ, Kỷ lục gia MAI ĐÌNH TỚI</t>
+  </si>
+  <si>
+    <t>Tiến sĩ, Kỷ lục gia NGÔ HỒ ANH KHÔI</t>
+  </si>
+  <si>
+    <t>KLG. Nhà thư pháp Lê Thiên Lý</t>
+  </si>
+  <si>
+    <t>KLG. Nguyễn Xuân Phương</t>
+  </si>
+  <si>
+    <t>KLG. Mai Quang Văn</t>
+  </si>
+  <si>
+    <t>CHỐT ĐẾN NGÀY 3.9</t>
+  </si>
+  <si>
+    <t>KLG Hồ Tất Và</t>
+  </si>
+  <si>
+    <t>KLG La Hưng (Tên thật: Trần Văn Khi)</t>
+  </si>
+  <si>
+    <t>KLG LÊ MINH PHÚ</t>
+  </si>
+  <si>
+    <t>Đại tá, Nhà báo TRẦN THẾ TUYỂN</t>
+  </si>
+  <si>
+    <t>Ông NGUYỄN THANH HẢI</t>
+  </si>
+  <si>
+    <t>Ông NGUYỄN HỮU ĐỈNH</t>
+  </si>
+  <si>
+    <t>Ông VÕ VĂN TÂM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bà: PHẠM THỊ TRÚC THI
+(Bút danh: TRÚC THY)</t>
+  </si>
+  <si>
+    <t>Ông Trần Quang Huy</t>
+  </si>
+  <si>
+    <t>Ông NGUYỄN ĐỨC TÀI (TÀI ALEX)</t>
+  </si>
+  <si>
+    <t>Ông Nguyễn Văn Nghỉ</t>
+  </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -7858,13 +8350,54 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FF081B3A"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7889,61 +8422,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF17365D"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4CCCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF17365D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -8034,7 +8537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -8162,38 +8665,83 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8212,7 +8760,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -8532,20 +9080,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <sheets>
-    <sheet sheetId="1" name="DANH SÁCH 560 NGƯỜI DEV XUẤT VỀ" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="200 người đã chuẩn" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="KẾT QUẢ 200 vs 560" state="visible" r:id="rId6"/>
-  </sheets>
-  <calcPr calcId="171027"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -44932,7 +45467,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA946"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -73300,1090 +73835,680 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="5" max="6" width="42.142857142857146" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="8" width="52" customWidth="1"/>
+    <col min="8" max="8" width="42.142857142857146" customWidth="1"/>
+    <col min="9" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KẾT QUẢ ĐỐI CHIẾU NGƯỜI TRONG TAB 200 VỚI DANH SÁCH 560</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tổng 24 người | Có trong 560: 17 | Cần kiểm tra: 1 | Không tìm thấy: 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xanh = có trong 560; vàng = tên gần giống cần xác nhận; đỏ = chưa tìm thấy. Ưu tiên kết quả khớp bằng link GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="8" customHeight="1"/>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STT</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TÊN TRONG TAB 200</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KẾT QUẢ</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TÊN TƯƠNG ỨNG TRONG 560</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINK GAB TAB 200</t>
-        </is>
-      </c>
-      <c r="F5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINK GAB TRONG 560</t>
-        </is>
-      </c>
-      <c r="G5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CĂN CỨ ĐỐI CHIẾU</t>
-        </is>
-      </c>
-      <c r="H5" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GHI CHÚ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN THỊ KIM THOA</t>
-        </is>
-      </c>
-      <c r="C6" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CẦN KIỂM TRA</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN KIM THOA</t>
-        </is>
-      </c>
-      <c r="E6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/IjcmvcxIRAQYlwmY6PWHBcUDHqt1</t>
-        </is>
-      </c>
-      <c r="F6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/l7fi9PXYDOeVaq8saBNw8PzjjR83</t>
-        </is>
-      </c>
-      <c r="G6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên gần giống 86%</t>
-        </is>
-      </c>
-      <c r="H6" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không tự kết luận là cùng người; cần kiểm tra thủ công.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ĐOÀN VĂN ĐỨC</t>
-        </is>
-      </c>
-      <c r="C7" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ĐOÀN VĂN ĐỨC</t>
-        </is>
-      </c>
-      <c r="E7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/3epGNJCJqgUBHRCm0ajy9lvl17z1</t>
-        </is>
-      </c>
-      <c r="F7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/3epGNJCJqgUBHRCm0ajy9lvl17z1</t>
-        </is>
-      </c>
-      <c r="G7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ NGUYỄN ÁI QUỲNH</t>
-        </is>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ NGUYỄN ÁI QUỲNH</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/xxExwFIb70VjkEsR8XS0tjsVBk92</t>
-        </is>
-      </c>
-      <c r="F8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/xxExwFIb70VjkEsR8XS0tjsVBk92</t>
-        </is>
-      </c>
-      <c r="G8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H8" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ QUỐC TOÀN</t>
-        </is>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ QUỐC TOÀN</t>
-        </is>
-      </c>
-      <c r="E9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/7vnbY6eDKKNdnkjwxsKCvPUFpdH3</t>
-        </is>
-      </c>
-      <c r="F9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/7vnbY6eDKKNdnkjwxsKCvPUFpdH3</t>
-        </is>
-      </c>
-      <c r="G9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H9" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ THỊ LỆ HẠNH</t>
-        </is>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ THỊ LỆ HẠNH</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/LOsM7ezziXOO2jUPjPH6TT7IROf2</t>
-        </is>
-      </c>
-      <c r="F10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/LOsM7ezziXOO2jUPjPH6TT7IROf2</t>
-        </is>
-      </c>
-      <c r="G10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H10" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ THIÊN LÝ</t>
-        </is>
-      </c>
-      <c r="C11" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LÊ THIÊN LÝ</t>
-        </is>
-      </c>
-      <c r="E11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/SsiHJ5KYUkNFf4lxqhej49v0BQj1</t>
-        </is>
-      </c>
-      <c r="F11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/SsiHJ5KYUkNFf4lxqhej49v0BQj1</t>
-        </is>
-      </c>
-      <c r="G11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H11" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN BÁ NHO</t>
-        </is>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN BÁ NHO</t>
-        </is>
-      </c>
-      <c r="E12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/DNuPNWjKRneZsr8shYSRiY94oav2</t>
-        </is>
-      </c>
-      <c r="F12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/DNuPNWjKRneZsr8shYSRiY94oav2</t>
-        </is>
-      </c>
-      <c r="G12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H12" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN HÙNG CƯỜNG</t>
-        </is>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN HÙNG CƯỜNG</t>
-        </is>
-      </c>
-      <c r="E13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/kzt3Ngoh4QSWNwJT9AbB7YwsVal1</t>
-        </is>
-      </c>
-      <c r="F13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/kzt3Ngoh4QSWNwJT9AbB7YwsVal1</t>
-        </is>
-      </c>
-      <c r="G13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H13" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN HUY DU</t>
-        </is>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN HUY DU</t>
-        </is>
-      </c>
-      <c r="E14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/zXQtcOoOwQdJyzbokThzW6KfS513</t>
-        </is>
-      </c>
-      <c r="F14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/zXQtcOoOwQdJyzbokThzW6KfS513</t>
-        </is>
-      </c>
-      <c r="G14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H14" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN LƯƠNG HIỆU</t>
-        </is>
-      </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN LƯƠNG HIỆU</t>
-        </is>
-      </c>
-      <c r="E15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/MObv8kj8KFZFZfFzgL8N0Q2SuNl1</t>
-        </is>
-      </c>
-      <c r="F15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/MObv8kj8KFZFZfFzgL8N0Q2SuNl1</t>
-        </is>
-      </c>
-      <c r="G15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H15" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN THANH THẢO</t>
-        </is>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN THANH THẢO</t>
-        </is>
-      </c>
-      <c r="E16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/iLBqqAeGazRoYLv93etx2HCuOwy1</t>
-        </is>
-      </c>
-      <c r="F16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/iLBqqAeGazRoYLv93etx2HCuOwy1</t>
-        </is>
-      </c>
-      <c r="G16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H16" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN VĂN VŨ AN</t>
-        </is>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN VĂN VŨ AN</t>
-        </is>
-      </c>
-      <c r="E17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/1MLatnsrcSUyHpolo0tFPp98xRh2</t>
-        </is>
-      </c>
-      <c r="F17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/1MLatnsrcSUyHpolo0tFPp98xRh2</t>
-        </is>
-      </c>
-      <c r="G17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHÙNG ĐẠI HÙNG</t>
-        </is>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHÙNG ĐẠI HÙNG</t>
-        </is>
-      </c>
-      <c r="E18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/erP8meGJOxPR9RkZaXLa24rpeHN2</t>
-        </is>
-      </c>
-      <c r="F18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/erP8meGJOxPR9RkZaXLa24rpeHN2</t>
-        </is>
-      </c>
-      <c r="G18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H18" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHÙNG HỮU THÁI</t>
-        </is>
-      </c>
-      <c r="C19" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHÙNG HỮU THÁI</t>
-        </is>
-      </c>
-      <c r="E19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/rQuYlosB59aYXhFuluTiyzJXUue2</t>
-        </is>
-      </c>
-      <c r="F19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/rQuYlosB59aYXhFuluTiyzJXUue2</t>
-        </is>
-      </c>
-      <c r="G19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H19" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRẦN ANH ĐIỀN</t>
-        </is>
-      </c>
-      <c r="C20" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRẦN ANH ĐIỀN</t>
-        </is>
-      </c>
-      <c r="E20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/bEKCaS06G1RFFywzGcQYRVDnSOj2</t>
-        </is>
-      </c>
-      <c r="F20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/bEKCaS06G1RFFywzGcQYRVDnSOj2</t>
-        </is>
-      </c>
-      <c r="G20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H20" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRẦN THỊ THU</t>
-        </is>
-      </c>
-      <c r="C21" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRẦN THỊ THU</t>
-        </is>
-      </c>
-      <c r="E21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/9jaJ5bFelZfXfZOygLcff0J4GX23</t>
-        </is>
-      </c>
-      <c r="F21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/9jaJ5bFelZfXfZOygLcff0J4GX23</t>
-        </is>
-      </c>
-      <c r="G21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H21" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRÚC PHƯƠNG</t>
-        </is>
-      </c>
-      <c r="C22" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRÚC PHƯƠNG</t>
-        </is>
-      </c>
-      <c r="E22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/zxBM0XX3MscGrapWaU21HeTBKmz2</t>
-        </is>
-      </c>
-      <c r="F22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/zxBM0XX3MscGrapWaU21HeTBKmz2</t>
-        </is>
-      </c>
-      <c r="G22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VI QUỐC HIỆP</t>
-        </is>
-      </c>
-      <c r="C23" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CÓ TRONG DANH SÁCH 560</t>
-        </is>
-      </c>
-      <c r="D23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VI QUỐC HIỆP</t>
-        </is>
-      </c>
-      <c r="E23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/Z6MR2ZsHsAOU8FiTkkYdcvwtbpl1</t>
-        </is>
-      </c>
-      <c r="F23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/Z6MR2ZsHsAOU8FiTkkYdcvwtbpl1</t>
-        </is>
-      </c>
-      <c r="G23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trùng chính xác link GAB</t>
-        </is>
-      </c>
-      <c r="H23" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đúng cùng một hồ sơ GAB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN VĂN BUÔI</t>
-        </is>
-      </c>
-      <c r="C24" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/GRartvX63gQH1iDWdARHaMmJ2it2</t>
-        </is>
-      </c>
-      <c r="F24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H24" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20</t>
-        </is>
-      </c>
-      <c r="B25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN VĂN HỮU</t>
-        </is>
-      </c>
-      <c r="C25" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/Kq6bMn0sRkXehHiPwziuvDfAfVb2</t>
-        </is>
-      </c>
-      <c r="F25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H25" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NGUYỄN VĂN NHÂN</t>
-        </is>
-      </c>
-      <c r="C26" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/zewNJIikXhW8OCj6imMqrrM6ogj1</t>
-        </is>
-      </c>
-      <c r="F26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H26" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHẠM S</t>
-        </is>
-      </c>
-      <c r="C27" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H27" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHAN THANH NHIÊN</t>
-        </is>
-      </c>
-      <c r="C28" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/RxBNnjdMn9hD4XjgCKcBNWuWyPH3</t>
-        </is>
-      </c>
-      <c r="F28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H28" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="B29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRẦN VĂN MẠNH</t>
-        </is>
-      </c>
-      <c r="C29" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHÔNG TÌM THẤY TRONG 560</t>
-        </is>
-      </c>
-      <c r="D29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://gab.world/vi/bank/GbScuk6rUlR0cEx2bIykg9EkG8z1</t>
-        </is>
-      </c>
-      <c r="F29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không có link hoặc tên khớp đủ chắc</t>
-        </is>
-      </c>
-      <c r="H29" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chưa thấy người tương ứng trong danh sách DEV xuất về.</t>
-        </is>
+    <row r="1" ht="27.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+    </row>
+    <row r="4" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>2576</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="6" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
+        <v>1</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>2581</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="7" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
+        <v>2</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>777</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>777</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>776</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>776</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="8" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="44">
+        <v>3</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="9" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
+        <v>4</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="10" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="44">
+        <v>5</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="11" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="44">
+        <v>6</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>1975</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="12" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="44">
+        <v>7</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>2082</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>2082</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="13" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="44">
+        <v>8</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="14" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="44">
+        <v>9</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="15" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="44">
+        <v>10</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="16" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="44">
+        <v>11</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>765</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>765</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>764</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>764</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="17" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="44">
+        <v>12</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>711</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>711</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>710</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>710</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="18" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="44">
+        <v>13</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F18" s="44" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="19" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="44">
+        <v>14</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="20" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="44">
+        <v>15</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="21" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="44">
+        <v>16</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F21" s="44" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="22" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="44">
+        <v>17</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F22" s="44" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="23" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="44">
+        <v>18</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="24" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="44">
+        <v>19</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="25" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="44">
+        <v>20</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44" t="s">
+        <v>2520</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="26" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="44">
+        <v>21</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="27" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="44">
+        <v>22</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="28" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="44">
+        <v>23</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="29" ht="39.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="44">
+        <v>24</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>2588</v>
       </c>
     </row>
   </sheetData>
@@ -74393,5 +74518,2673 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H136"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="27" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>2591</v>
+      </c>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="49" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="49" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="50" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="51">
+        <v>1</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
+        <v>2</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="51">
+        <v>3</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="51">
+        <v>4</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="51">
+        <v>5</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="51">
+        <v>6</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="51">
+        <v>7</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="51">
+        <v>8</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="56">
+        <v>9</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E11" s="60"/>
+      <c r="F11" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="51">
+        <v>10</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="51">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="53" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
+        <v>12</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="51">
+        <v>13</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
+        <v>14</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="51">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="53" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
+        <v>16</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="51">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="53" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="51">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="53" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D20" s="54" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="51">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="53" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="53" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="56">
+        <v>21</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="58" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E23" s="60"/>
+      <c r="F23" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="51">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="53" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="51">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="53" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="56">
+        <v>24</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="58" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="51">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="53" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="56">
+        <v>26</v>
+      </c>
+      <c r="B28" s="60"/>
+      <c r="C28" s="58" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="51">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="53" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="51">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="53" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="51">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="53" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="51">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="53" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="51">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="53" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="51">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="53" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="56">
+        <v>33</v>
+      </c>
+      <c r="B35" s="60"/>
+      <c r="C35" s="58" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D35" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E35" s="60"/>
+      <c r="F35" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="51">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="53" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="51">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="53" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="51">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="53" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="51">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="53" t="s">
+        <v>2646</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="51">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="53" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="51">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="53" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="51">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="53" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="56">
+        <v>41</v>
+      </c>
+      <c r="B43" s="60"/>
+      <c r="C43" s="58" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D43" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E43" s="60"/>
+      <c r="F43" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="51">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="53" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D44" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="56">
+        <v>43</v>
+      </c>
+      <c r="B45" s="60"/>
+      <c r="C45" s="58" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E45" s="60"/>
+      <c r="F45" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="51">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="53" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D46" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="51">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="53" t="s">
+        <v>2654</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="51">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="53" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="51">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="53" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D49" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="51">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="53" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D50" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="53" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D51" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="51">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="53" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D52" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="51">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="53" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D53" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="51">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="53" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D54" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="51">
+        <v>53</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="53" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D55" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="51">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="53" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D56" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="51">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="53" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="51">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="53" t="s">
+        <v>2665</v>
+      </c>
+      <c r="D58" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="51">
+        <v>57</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D59" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="56">
+        <v>58</v>
+      </c>
+      <c r="B60" s="60"/>
+      <c r="C60" s="58" t="s">
+        <v>2667</v>
+      </c>
+      <c r="D60" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E60" s="60"/>
+      <c r="F60" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="51">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="62" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D61" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="51">
+        <v>60</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="53" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D62" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="51">
+        <v>61</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="53" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D63" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="51">
+        <v>62</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="53" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D64" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="51">
+        <v>63</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="53" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D65" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="51">
+        <v>64</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="53" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D66" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="51">
+        <v>65</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="53" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D67" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="51">
+        <v>66</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="53" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D68" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E68" s="1"/>
+      <c r="F68" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="56">
+        <v>67</v>
+      </c>
+      <c r="B69" s="60"/>
+      <c r="C69" s="58" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D69" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E69" s="60"/>
+      <c r="F69" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="51">
+        <v>68</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="53" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D70" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E70" s="1"/>
+      <c r="F70" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="51">
+        <v>69</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="53" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D71" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="51">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="53" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D72" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E72" s="1"/>
+      <c r="F72" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="51">
+        <v>71</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="53" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D73" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E73" s="1"/>
+      <c r="F73" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="56">
+        <v>72</v>
+      </c>
+      <c r="B74" s="60"/>
+      <c r="C74" s="58" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D74" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E74" s="60"/>
+      <c r="F74" s="61" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="51">
+        <v>73</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="53" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D75" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E75" s="1"/>
+      <c r="F75" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="56">
+        <v>74</v>
+      </c>
+      <c r="B76" s="60"/>
+      <c r="C76" s="58" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D76" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E76" s="60"/>
+      <c r="F76" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="51">
+        <v>75</v>
+      </c>
+      <c r="B77" s="1"/>
+      <c r="C77" s="53" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D77" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E77" s="1"/>
+      <c r="F77" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="51">
+        <v>76</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="53" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D78" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="51">
+        <v>77</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="53" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D79" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="51">
+        <v>78</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="53" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D80" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="51">
+        <v>79</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="53" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D81" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="51">
+        <v>80</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="53" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D82" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="51">
+        <v>81</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="53" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D83" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="51">
+        <v>82</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="53" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D84" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="51">
+        <v>83</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="53" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D85" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="51">
+        <v>84</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="53" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D86" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G86" s="1"/>
+      <c r="H86" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="56">
+        <v>85</v>
+      </c>
+      <c r="B87" s="60"/>
+      <c r="C87" s="58" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D87" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E87" s="60"/>
+      <c r="F87" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="56">
+        <v>86</v>
+      </c>
+      <c r="B88" s="63"/>
+      <c r="C88" s="64" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D88" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G88" s="1"/>
+      <c r="H88" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="51">
+        <v>87</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="53" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D89" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E89" s="1"/>
+      <c r="F89" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G89" s="1"/>
+      <c r="H89" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="51">
+        <v>88</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="53" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D90" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E90" s="1"/>
+      <c r="F90" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G90" s="1"/>
+      <c r="H90" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="51">
+        <v>89</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="53" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D91" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="51">
+        <v>90</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="53" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D92" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E92" s="1"/>
+      <c r="F92" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="51">
+        <v>91</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="53" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D93" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E93" s="1"/>
+      <c r="F93" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G93" s="1"/>
+      <c r="H93" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="51">
+        <v>92</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="53" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D94" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E94" s="1"/>
+      <c r="F94" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="51">
+        <v>93</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="53" t="s">
+        <v>2702</v>
+      </c>
+      <c r="D95" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E95" s="1"/>
+      <c r="F95" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="51">
+        <v>94</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="53" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D96" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E96" s="1"/>
+      <c r="F96" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="51">
+        <v>95</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="53" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D97" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="51">
+        <v>96</v>
+      </c>
+      <c r="B98" s="1"/>
+      <c r="C98" s="53" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D98" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E98" s="1"/>
+      <c r="F98" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G98" s="1"/>
+      <c r="H98" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="51">
+        <v>97</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="53" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D99" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E99" s="1"/>
+      <c r="F99" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G99" s="1"/>
+      <c r="H99" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="51">
+        <v>98</v>
+      </c>
+      <c r="B100" s="1"/>
+      <c r="C100" s="53" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D100" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G100" s="1"/>
+      <c r="H100" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="51">
+        <v>99</v>
+      </c>
+      <c r="B101" s="1"/>
+      <c r="C101" s="53" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D101" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E101" s="1"/>
+      <c r="F101" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="51">
+        <v>100</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="65" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D102" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E102" s="1"/>
+      <c r="F102" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="51">
+        <v>101</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="53" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D103" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E103" s="1"/>
+      <c r="F103" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="51">
+        <v>102</v>
+      </c>
+      <c r="B104" s="1"/>
+      <c r="C104" s="53" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D104" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E104" s="1"/>
+      <c r="F104" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G104" s="1"/>
+      <c r="H104" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="51">
+        <v>103</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="53" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D105" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="51">
+        <v>104</v>
+      </c>
+      <c r="B106" s="1"/>
+      <c r="C106" s="53" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D106" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E106" s="1"/>
+      <c r="F106" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="51">
+        <v>105</v>
+      </c>
+      <c r="B107" s="1"/>
+      <c r="C107" s="53" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D107" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E107" s="1"/>
+      <c r="F107" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="51">
+        <v>106</v>
+      </c>
+      <c r="B108" s="1"/>
+      <c r="C108" s="53" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D108" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="51">
+        <v>107</v>
+      </c>
+      <c r="B109" s="1"/>
+      <c r="C109" s="53" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D109" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E109" s="1"/>
+      <c r="F109" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="56">
+        <v>108</v>
+      </c>
+      <c r="B110" s="1"/>
+      <c r="C110" s="25" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D110" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E110" s="1"/>
+      <c r="F110" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G110" s="1"/>
+      <c r="H110" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="51">
+        <v>109</v>
+      </c>
+      <c r="B111" s="1"/>
+      <c r="C111" s="53" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D111" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E111" s="1"/>
+      <c r="F111" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G111" s="1"/>
+      <c r="H111" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="51">
+        <v>110</v>
+      </c>
+      <c r="B112" s="1"/>
+      <c r="C112" s="66" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D112" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E112" s="1"/>
+      <c r="F112" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="51">
+        <v>111</v>
+      </c>
+      <c r="B113" s="1"/>
+      <c r="C113" s="66" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D113" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E113" s="1"/>
+      <c r="F113" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G113" s="1"/>
+      <c r="H113" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="51">
+        <v>112</v>
+      </c>
+      <c r="B114" s="1"/>
+      <c r="C114" s="66" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D114" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E114" s="1"/>
+      <c r="F114" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G114" s="1"/>
+      <c r="H114" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="56">
+        <v>113</v>
+      </c>
+      <c r="B115" s="60"/>
+      <c r="C115" s="67" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D115" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E115" s="60"/>
+      <c r="F115" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="51">
+        <v>114</v>
+      </c>
+      <c r="B116" s="1"/>
+      <c r="C116" s="66" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D116" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E116" s="1"/>
+      <c r="F116" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G116" s="1"/>
+      <c r="H116" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="56">
+        <v>115</v>
+      </c>
+      <c r="B117" s="60"/>
+      <c r="C117" s="67" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D117" s="59" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E117" s="60"/>
+      <c r="F117" s="61" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G117" s="1"/>
+      <c r="H117" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="51">
+        <v>116</v>
+      </c>
+      <c r="B118" s="1"/>
+      <c r="C118" s="66" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D118" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E118" s="1"/>
+      <c r="F118" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="51">
+        <v>117</v>
+      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="66" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D119" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E119" s="1"/>
+      <c r="F119" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="51">
+        <v>118</v>
+      </c>
+      <c r="B120" s="1"/>
+      <c r="C120" s="66" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D120" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E120" s="1"/>
+      <c r="F120" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G120" s="1"/>
+      <c r="H120" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="51">
+        <v>119</v>
+      </c>
+      <c r="B121" s="1"/>
+      <c r="C121" s="66" t="s">
+        <v>2728</v>
+      </c>
+      <c r="D121" s="54" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E121" s="1"/>
+      <c r="F121" s="55" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G121" s="1"/>
+      <c r="H121" s="55" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="68" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B122" s="68"/>
+      <c r="C122" s="68"/>
+      <c r="D122" s="68"/>
+      <c r="E122" s="68"/>
+      <c r="F122" s="68"/>
+      <c r="G122" s="68"/>
+      <c r="H122" s="1"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="51">
+        <v>120</v>
+      </c>
+      <c r="B123" s="1"/>
+      <c r="C123" s="66" t="s">
+        <v>2730</v>
+      </c>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="51">
+        <v>121</v>
+      </c>
+      <c r="B124" s="1"/>
+      <c r="C124" s="66" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="51">
+        <v>122</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="66" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="51">
+        <v>123</v>
+      </c>
+      <c r="B126" s="1"/>
+      <c r="C126" s="66" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="51">
+        <v>124</v>
+      </c>
+      <c r="B127" s="1"/>
+      <c r="C127" s="66" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="51">
+        <v>125</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="66" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="51">
+        <v>126</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="66" t="s">
+        <v>2734</v>
+      </c>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="51">
+        <v>127</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="66" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="51">
+        <v>128</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="66" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="51">
+        <v>129</v>
+      </c>
+      <c r="B132" s="1"/>
+      <c r="C132" s="66" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="51">
+        <v>130</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="66" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="51">
+        <v>131</v>
+      </c>
+      <c r="B134" s="1"/>
+      <c r="C134" s="66" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="51">
+        <v>132</v>
+      </c>
+      <c r="B135" s="1"/>
+      <c r="C135" s="66" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="51">
+        <v>133</v>
+      </c>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="A122:G122"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>